--- a/skyscanner_tulokset.xlsx
+++ b/skyscanner_tulokset.xlsx
@@ -1,34 +1,164 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2847b1d23e757949/Tiedostot/RPA - Smart travel agent/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6307E68F797866FD10EDA39874D2F59FC0DAFD1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74AEF66B-F8AA-4AF4-BE6E-4B3AC7F200DF}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="9030" yWindow="2700" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Hotellit" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+  <si>
+    <t>Sija</t>
+  </si>
+  <si>
+    <t>Hotelli</t>
+  </si>
+  <si>
+    <t>Hinta</t>
+  </si>
+  <si>
+    <t>Arvostelu</t>
+  </si>
+  <si>
+    <t>Linkki</t>
+  </si>
+  <si>
+    <t>Hakupäivä</t>
+  </si>
+  <si>
+    <t>HotelHome Paris 16</t>
+  </si>
+  <si>
+    <t>1230</t>
+  </si>
+  <si>
+    <t>8,6</t>
+  </si>
+  <si>
+    <t>https://www.trivago.fi/forward/fi?forwarderA=pNnwtMIwnaXyRE0By8i2j4VFPT2ssttTf73s5JMIy3iceUxUXB%2BToiCqRIU5NyTR3ljfmO87dbdZwV3g5gtQaE%2BCUzqa8j0dSLR6wa3Sz8KdaLQs60SIZNxIwgbxUJ8nEujNl55haB41Re9UzIZhNK%2B6JKL5xrkXc778KjP%2BiV7GHpApeArox4RSgGrYKGg%2F8AVbHLK0Lip02CSGdnR87fcETPDqF01Ql8wy%2BRkINcCGMoOm8JQpGj4ddDYKLuOD%2B17WBkW7MZ7vqrwpDhgrDMt7kG2royfPIAXix8cFeHIyVScJ%2Fln87J9Vv%2Fnq%2FBx7nsXRvlNd7GkdnCB4s0xJmfMVtoyRqZi20yENGs4MCRXysh0Ucg1dDOpAy4JR2vqcwsQNN2Q9tV6bXEDgbaDJ702KEnY4uXjU1vSrXmxnJk6HGCGP1hRuZNYk0y9q&amp;forwarderB=ztPfUKp8Qw8agarBKFN%2B9enulpdAZFmUOzjaHsSpX3KX5mxmwM0%2FKlDDEs01Kmb6JbdrXQ1D3L52U3%2BiEuM6I7%2F8HjnRphLW1dAPBYpTkSwIZi%2F%2FFE3ZbFGe14OwLZ9ffhFko4jgv8JiVqxQMJpxPBKIX0L4uOtLFN2qKrtg%2FUB%2BB18j%2BJB5%2FcfuybDFEL8XENWtNA76jJDndiQ1R0clXeieogeHr8zczP3iVGoJ5Sk%2B18tane9fOutUGSR5rMMRqDehvRZtuNlHJlFslnCMHd2s7RUAN%2Bks1Ns%2FXJE8gny%2FmA%2BsOqIYBYjhJVsd%2BchWm74ayds3J0vJIyRO5T9ykvpt%2FgAeJpvkiaCwn%2Byt%2BNs%2BklC8u90ZUW6NDlmvmrNGc%2BeJCsMid8WwMK00YLKw2yswzyYM9tDyYOI%3D&amp;forwarderC=JTdCJTIyYWNjb21tb2RhdGlvblBvc2l0aW9uJTIyJTNBMSUyQyUyMmxpbmtMb2NhdGlvbiUyMiUzQSUyMkNIQU1QSU9OX0RFQUwlMjIlMkMlMjJwYWdlQ29udGFpbmVyJTIyJTNBJTIyTUFJTiUyMiUyQyUyMnBhZ2VOdW1iZXIlMjIlM0ExJTJDJTIydmlld01vZGUlMjIlM0ElMjJTVEFOREFSRCUyMiUyQyUyMmNsaWNrb3V0U291cmNlJTIyJTNBJTIySVRFTV9MSVNUX0NIQU1QSU9OX0RFQUwlMjIlMkMlMjJjbGllbnRDb25uZWN0aW9uSWQlMjIlM0ElMjJXemJxTzFyUXhBbFhhMjExY1BSRkh2cnlIMFclMjIlMkMlMjJjbGllbnRTZXF1ZW5jZUlkJTIyJTNBMjIwJTJDJTIyY2xpY2tvdXRFdmVudElkJTIyJTNBJTIyNTMwZTJmOGEtYTNkNC00YThlLTlmMmQtYTVhY2VkMDdjYWE0JTIyJTdE</t>
+  </si>
+  <si>
+    <t>06.04.2026</t>
+  </si>
+  <si>
+    <t>Aparthotel Adagio Paris Nation</t>
+  </si>
+  <si>
+    <t>1176</t>
+  </si>
+  <si>
+    <t>https://www.trivago.fi/forward/fi?forwarderA=E8ccvYMGeRF5T3vjOfROVQf00GZ%2BuXfqTkwlkhgUqhuE79tx2RO%2FUhlNbgoOq9c2Jdgo%2BlKip0V9Zj9xSIjz8H5iIetixoa43QN8v%2F%2FIQghwIREKyQGkDTrKPjpotldZe648wVeu7aP9yxiKPsIK1wuJ20atoxd5wGmeKAYIJpGLGvd9ZJkqIseVyL8tZIBAKNoVFMJlozHYPX9orewhf09fCbTHOdyOc%2FRysAMKUC5wM5yjiMsItjcW9OGPAb0u1%2FHIsdN%2BKrl05l9vTy4RlH1lubYsH7mxxkyaXpif1h0NR9ukxpjL1BHwuj%2BJp%2FpBfEvcENa6xNiW4lyrX2B%2FqCqJOmb%2B%2F4SPNoPulna2OFCXb8r8%2BIvbJO551%2FHSYB5NEqJc9DC3ILLFyMF4l5TDu6L7y%2B3IHviRYtetA8nKMX34%2BpjrKS7RdLhImfzs&amp;forwarderB=R%2BFIhWMk6feKclOU%2BXfs6VYqCPOcBFpk6RNvCzQcuy4hc7A5ihHmNlip4aOuE%2BjzWTtNyTCZD4bLNsNaovc6%2BJ6dk%2BCHBg%2B%2BOEYjTwqcgcjkS3IB7a%2FPmEsU032ttdql8oRG8XckR2bTEOj93QVPe16Uc04O7KC3wZWRKY79y6uHBGwkx1UUFWPZuDkFbg%2BDbHr9VAFjFZ4EhjnMbKMXB1g38MUwsmrrsSf%2BU%2BCvibVCfLOp%2Bml6B92JJRcdfN%2FOTZ9fG3ZxYdbF7GUtkHQAGZ3iMRMHPShL%2BNTGJVBHNL1RDmic5Tv%2FbeUrXWNzHSQh0LgPn7oNghUdUHysgKpITUnFiWB0NTRkldVP7Swt2JNiEfvKUEV2p6OVYXyUgc%2BO6YkZO1pABjWDJRcwUbUTKsqV1fPrP%2Fesva%2BIeOYt4%2F1K&amp;forwarderC=JTdCJTIyYWNjb21tb2RhdGlvblBvc2l0aW9uJTIyJTNBMiUyQyUyMmxpbmtMb2NhdGlvbiUyMiUzQSUyMkNIQU1QSU9OX0RFQUwlMjIlMkMlMjJwYWdlQ29udGFpbmVyJTIyJTNBJTIyTUFJTiUyMiUyQyUyMnBhZ2VOdW1iZXIlMjIlM0ExJTJDJTIydmlld01vZGUlMjIlM0ElMjJTVEFOREFSRCUyMiUyQyUyMmNsaWNrb3V0U291cmNlJTIyJTNBJTIySVRFTV9MSVNUX0NIQU1QSU9OX0RFQUwlMjIlMkMlMjJjbGllbnRDb25uZWN0aW9uSWQlMjIlM0ElMjJXemJxTzFyUXhBbFhhMjExY1BSRkh2cnlIMFclMjIlMkMlMjJjbGllbnRTZXF1ZW5jZUlkJTIyJTNBMjI0JTJDJTIyY2xpY2tvdXRFdmVudElkJTIyJTNBJTIyM2Q4MmQ2NTUtZDk2ZC00N2ZhLTg3MDMtYTM3ODczYmNjYzY4JTIyJTdE</t>
+  </si>
+  <si>
+    <t>Edgar Suites Expo Paris Porte de Versailles</t>
+  </si>
+  <si>
+    <t>1307</t>
+  </si>
+  <si>
+    <t>9,2</t>
+  </si>
+  <si>
+    <t>https://www.trivago.fi/forward/fi?forwarderA=HQ9bOB3mzf5p6vAKAvH432NpeD5455JUE%2F7AsqCtmOQlVlX1KhtmckGc7w08eiA4YfhYIjoeSzr6XgAr3nWi4XUqRVAlq5ah6DoS6q3DnPKCWW2J2PwvGB5IQHRUaPeDXUDXOK3OFrQhJk3qMELmNOC2Fhl0FrnXdqyTmi7exd5KFHlR5auGYwQyzEXO%2FgrL6oxGYhm08l3LtpyDQ5GOxsDUc2GpKA9JrSe497YpWSPUcr6fHxIb4cyQrQL8wZtuBjLv3fBCT12BO5C46sq9gun3cn8PnGv3wM06nZvrXs6uvfWQMQXtdUhj%2BSaU3nyfwnKcCR9iYZPpOq%2F7C%2FjSKS3QYHKlaOT6ORyuYzHXAL1%2FcrRINax34T8cYqi3KEjzxY%2FOqzDI2uveKAaTeq3XrA2AmaU%2BfnhnZn7IS8PCorq5wuPos%2BSITNc73e5B&amp;forwarderB=676xMcbxV9bowJw5ZfEXrZ02wh3rHgwnqoLAZcQvbfVFDZBOrIwsK75OCd%2BIPNYJPX%2B3WGPTNH6IkNQIL7i%2FfbCQ0QZuWwkvyTSAo6bC5jHh%2BkAz4i0kwQAS3GrHZgTpd%2BfhmwYBdK6UxFLFvnSThAfWylLUs4Tr%2B6862iU3pVuywtpb0%2FLGT5LAoPfEG%2FhAd%2BxKa%2BXPqX9ZivuFpXbtmFKltC6WdZCdVnq%2BZn7qhQj0ZPvx%2BoGTfeLkxjRpGHowXrYpUUkt5lPOTAus%2F1kanfYLU%2FBqWPhufk4IGtTjT9rGZhoZQcxHwxNri4kZanmcdA%2BrvdaF1iJtIh8HMKBKe7vUrth2rC7qHk63b%2BFEyhlvMEajHWw6zPhZOmrQkFteapAnKvXwIBoV149uqVGIJC8byFo9T0XnMRJ9Bg%3D%3D&amp;forwarderC=JTdCJTIyYWNjb21tb2RhdGlvblBvc2l0aW9uJTIyJTNBMyUyQyUyMmxpbmtMb2NhdGlvbiUyMiUzQSUyMkNIQU1QSU9OX0RFQUwlMjIlMkMlMjJwYWdlQ29udGFpbmVyJTIyJTNBJTIyTUFJTiUyMiUyQyUyMnBhZ2VOdW1iZXIlMjIlM0ExJTJDJTIydmlld01vZGUlMjIlM0ElMjJTVEFOREFSRCUyMiUyQyUyMmNsaWNrb3V0U291cmNlJTIyJTNBJTIySVRFTV9MSVNUX0NIQU1QSU9OX0RFQUwlMjIlMkMlMjJjbGllbnRDb25uZWN0aW9uSWQlMjIlM0ElMjJXemJxTzFyUXhBbFhhMjExY1BSRkh2cnlIMFclMjIlMkMlMjJjbGllbnRTZXF1ZW5jZUlkJTIyJTNBMjI4JTJDJTIyY2xpY2tvdXRFdmVudElkJTIyJTNBJTIyZTNiODljMWYtMWYxMy00Y2NlLTliYWMtMzU4ZTVkM2IyZmUyJTIyJTdE</t>
+  </si>
+  <si>
+    <t>Lentoyhtiö</t>
+  </si>
+  <si>
+    <t>Meno lähtee</t>
+  </si>
+  <si>
+    <t>Meno perillä</t>
+  </si>
+  <si>
+    <t>Paluu lähtee</t>
+  </si>
+  <si>
+    <t>Paluu perillä</t>
+  </si>
+  <si>
+    <t>Kokonaishinta (4 hlö)</t>
+  </si>
+  <si>
+    <t>Varauslinkki</t>
+  </si>
+  <si>
+    <t>Finnair</t>
+  </si>
+  <si>
+    <t>12.15</t>
+  </si>
+  <si>
+    <t>14.20</t>
+  </si>
+  <si>
+    <t>12.35</t>
+  </si>
+  <si>
+    <t>16.40</t>
+  </si>
+  <si>
+    <t>969 €</t>
+  </si>
+  <si>
+    <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221235--32317-0-12126-2608221640?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
+  </si>
+  <si>
+    <t>20.30</t>
+  </si>
+  <si>
+    <t>22.35</t>
+  </si>
+  <si>
+    <t>822 €</t>
+  </si>
+  <si>
+    <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608152030--32317-0-10413-2608152235%7C10413-2608221235--32317-0-12126-2608221640?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
+  </si>
+  <si>
+    <t>15.05</t>
+  </si>
+  <si>
+    <t>19.00</t>
+  </si>
+  <si>
+    <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221505--32317-0-12126-2608221900?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +176,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normaali" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,114 +480,220 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sija</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Lentoyhtiö</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Kokonaishinta (4 hlö)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Varauslinkki</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Hakupäivä</t>
-        </is>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Finnair</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>969 €</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221235--32317-0-12126-2608221640?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>06.04.2026</t>
-        </is>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Finnair</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1 049 €</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221505--32317-0-12126-2608221900?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>06.04.2026</t>
-        </is>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Finnair</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1 073 €</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221900--32317-0-12126-2608222255?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>06.04.2026</t>
-        </is>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1049</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/skyscanner_tulokset.xlsx
+++ b/skyscanner_tulokset.xlsx
@@ -8,96 +8,47 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2847b1d23e757949/Tiedostot/RPA - Smart travel agent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_6307E68F797866FD10EDA39874D2F59FC0DAFD1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74AEF66B-F8AA-4AF4-BE6E-4B3AC7F200DF}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_AB58FBE7504A22CFEB3B98154B1626B968C7FEEC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06E05AEE-03B0-4DF2-878F-78287689E0D0}"/>
   <bookViews>
-    <workbookView xWindow="9030" yWindow="2700" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="4260" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
-    <sheet name="Hotellit" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>Sija</t>
   </si>
   <si>
-    <t>Hotelli</t>
-  </si>
-  <si>
-    <t>Hinta</t>
-  </si>
-  <si>
-    <t>Arvostelu</t>
-  </si>
-  <si>
-    <t>Linkki</t>
+    <t>Lentoyhtiö</t>
+  </si>
+  <si>
+    <t>Meno lähtee</t>
+  </si>
+  <si>
+    <t>Meno perillä</t>
+  </si>
+  <si>
+    <t>Paluu lähtee</t>
+  </si>
+  <si>
+    <t>Paluu perillä</t>
+  </si>
+  <si>
+    <t>Kokonaishinta (4 hlö)</t>
+  </si>
+  <si>
+    <t>Varauslinkki</t>
   </si>
   <si>
     <t>Hakupäivä</t>
   </si>
   <si>
-    <t>HotelHome Paris 16</t>
-  </si>
-  <si>
-    <t>1230</t>
-  </si>
-  <si>
-    <t>8,6</t>
-  </si>
-  <si>
-    <t>https://www.trivago.fi/forward/fi?forwarderA=pNnwtMIwnaXyRE0By8i2j4VFPT2ssttTf73s5JMIy3iceUxUXB%2BToiCqRIU5NyTR3ljfmO87dbdZwV3g5gtQaE%2BCUzqa8j0dSLR6wa3Sz8KdaLQs60SIZNxIwgbxUJ8nEujNl55haB41Re9UzIZhNK%2B6JKL5xrkXc778KjP%2BiV7GHpApeArox4RSgGrYKGg%2F8AVbHLK0Lip02CSGdnR87fcETPDqF01Ql8wy%2BRkINcCGMoOm8JQpGj4ddDYKLuOD%2B17WBkW7MZ7vqrwpDhgrDMt7kG2royfPIAXix8cFeHIyVScJ%2Fln87J9Vv%2Fnq%2FBx7nsXRvlNd7GkdnCB4s0xJmfMVtoyRqZi20yENGs4MCRXysh0Ucg1dDOpAy4JR2vqcwsQNN2Q9tV6bXEDgbaDJ702KEnY4uXjU1vSrXmxnJk6HGCGP1hRuZNYk0y9q&amp;forwarderB=ztPfUKp8Qw8agarBKFN%2B9enulpdAZFmUOzjaHsSpX3KX5mxmwM0%2FKlDDEs01Kmb6JbdrXQ1D3L52U3%2BiEuM6I7%2F8HjnRphLW1dAPBYpTkSwIZi%2F%2FFE3ZbFGe14OwLZ9ffhFko4jgv8JiVqxQMJpxPBKIX0L4uOtLFN2qKrtg%2FUB%2BB18j%2BJB5%2FcfuybDFEL8XENWtNA76jJDndiQ1R0clXeieogeHr8zczP3iVGoJ5Sk%2B18tane9fOutUGSR5rMMRqDehvRZtuNlHJlFslnCMHd2s7RUAN%2Bks1Ns%2FXJE8gny%2FmA%2BsOqIYBYjhJVsd%2BchWm74ayds3J0vJIyRO5T9ykvpt%2FgAeJpvkiaCwn%2Byt%2BNs%2BklC8u90ZUW6NDlmvmrNGc%2BeJCsMid8WwMK00YLKw2yswzyYM9tDyYOI%3D&amp;forwarderC=JTdCJTIyYWNjb21tb2RhdGlvblBvc2l0aW9uJTIyJTNBMSUyQyUyMmxpbmtMb2NhdGlvbiUyMiUzQSUyMkNIQU1QSU9OX0RFQUwlMjIlMkMlMjJwYWdlQ29udGFpbmVyJTIyJTNBJTIyTUFJTiUyMiUyQyUyMnBhZ2VOdW1iZXIlMjIlM0ExJTJDJTIydmlld01vZGUlMjIlM0ElMjJTVEFOREFSRCUyMiUyQyUyMmNsaWNrb3V0U291cmNlJTIyJTNBJTIySVRFTV9MSVNUX0NIQU1QSU9OX0RFQUwlMjIlMkMlMjJjbGllbnRDb25uZWN0aW9uSWQlMjIlM0ElMjJXemJxTzFyUXhBbFhhMjExY1BSRkh2cnlIMFclMjIlMkMlMjJjbGllbnRTZXF1ZW5jZUlkJTIyJTNBMjIwJTJDJTIyY2xpY2tvdXRFdmVudElkJTIyJTNBJTIyNTMwZTJmOGEtYTNkNC00YThlLTlmMmQtYTVhY2VkMDdjYWE0JTIyJTdE</t>
-  </si>
-  <si>
-    <t>06.04.2026</t>
-  </si>
-  <si>
-    <t>Aparthotel Adagio Paris Nation</t>
-  </si>
-  <si>
-    <t>1176</t>
-  </si>
-  <si>
-    <t>https://www.trivago.fi/forward/fi?forwarderA=E8ccvYMGeRF5T3vjOfROVQf00GZ%2BuXfqTkwlkhgUqhuE79tx2RO%2FUhlNbgoOq9c2Jdgo%2BlKip0V9Zj9xSIjz8H5iIetixoa43QN8v%2F%2FIQghwIREKyQGkDTrKPjpotldZe648wVeu7aP9yxiKPsIK1wuJ20atoxd5wGmeKAYIJpGLGvd9ZJkqIseVyL8tZIBAKNoVFMJlozHYPX9orewhf09fCbTHOdyOc%2FRysAMKUC5wM5yjiMsItjcW9OGPAb0u1%2FHIsdN%2BKrl05l9vTy4RlH1lubYsH7mxxkyaXpif1h0NR9ukxpjL1BHwuj%2BJp%2FpBfEvcENa6xNiW4lyrX2B%2FqCqJOmb%2B%2F4SPNoPulna2OFCXb8r8%2BIvbJO551%2FHSYB5NEqJc9DC3ILLFyMF4l5TDu6L7y%2B3IHviRYtetA8nKMX34%2BpjrKS7RdLhImfzs&amp;forwarderB=R%2BFIhWMk6feKclOU%2BXfs6VYqCPOcBFpk6RNvCzQcuy4hc7A5ihHmNlip4aOuE%2BjzWTtNyTCZD4bLNsNaovc6%2BJ6dk%2BCHBg%2B%2BOEYjTwqcgcjkS3IB7a%2FPmEsU032ttdql8oRG8XckR2bTEOj93QVPe16Uc04O7KC3wZWRKY79y6uHBGwkx1UUFWPZuDkFbg%2BDbHr9VAFjFZ4EhjnMbKMXB1g38MUwsmrrsSf%2BU%2BCvibVCfLOp%2Bml6B92JJRcdfN%2FOTZ9fG3ZxYdbF7GUtkHQAGZ3iMRMHPShL%2BNTGJVBHNL1RDmic5Tv%2FbeUrXWNzHSQh0LgPn7oNghUdUHysgKpITUnFiWB0NTRkldVP7Swt2JNiEfvKUEV2p6OVYXyUgc%2BO6YkZO1pABjWDJRcwUbUTKsqV1fPrP%2Fesva%2BIeOYt4%2F1K&amp;forwarderC=JTdCJTIyYWNjb21tb2RhdGlvblBvc2l0aW9uJTIyJTNBMiUyQyUyMmxpbmtMb2NhdGlvbiUyMiUzQSUyMkNIQU1QSU9OX0RFQUwlMjIlMkMlMjJwYWdlQ29udGFpbmVyJTIyJTNBJTIyTUFJTiUyMiUyQyUyMnBhZ2VOdW1iZXIlMjIlM0ExJTJDJTIydmlld01vZGUlMjIlM0ElMjJTVEFOREFSRCUyMiUyQyUyMmNsaWNrb3V0U291cmNlJTIyJTNBJTIySVRFTV9MSVNUX0NIQU1QSU9OX0RFQUwlMjIlMkMlMjJjbGllbnRDb25uZWN0aW9uSWQlMjIlM0ElMjJXemJxTzFyUXhBbFhhMjExY1BSRkh2cnlIMFclMjIlMkMlMjJjbGllbnRTZXF1ZW5jZUlkJTIyJTNBMjI0JTJDJTIyY2xpY2tvdXRFdmVudElkJTIyJTNBJTIyM2Q4MmQ2NTUtZDk2ZC00N2ZhLTg3MDMtYTM3ODczYmNjYzY4JTIyJTdE</t>
-  </si>
-  <si>
-    <t>Edgar Suites Expo Paris Porte de Versailles</t>
-  </si>
-  <si>
-    <t>1307</t>
-  </si>
-  <si>
-    <t>9,2</t>
-  </si>
-  <si>
-    <t>https://www.trivago.fi/forward/fi?forwarderA=HQ9bOB3mzf5p6vAKAvH432NpeD5455JUE%2F7AsqCtmOQlVlX1KhtmckGc7w08eiA4YfhYIjoeSzr6XgAr3nWi4XUqRVAlq5ah6DoS6q3DnPKCWW2J2PwvGB5IQHRUaPeDXUDXOK3OFrQhJk3qMELmNOC2Fhl0FrnXdqyTmi7exd5KFHlR5auGYwQyzEXO%2FgrL6oxGYhm08l3LtpyDQ5GOxsDUc2GpKA9JrSe497YpWSPUcr6fHxIb4cyQrQL8wZtuBjLv3fBCT12BO5C46sq9gun3cn8PnGv3wM06nZvrXs6uvfWQMQXtdUhj%2BSaU3nyfwnKcCR9iYZPpOq%2F7C%2FjSKS3QYHKlaOT6ORyuYzHXAL1%2FcrRINax34T8cYqi3KEjzxY%2FOqzDI2uveKAaTeq3XrA2AmaU%2BfnhnZn7IS8PCorq5wuPos%2BSITNc73e5B&amp;forwarderB=676xMcbxV9bowJw5ZfEXrZ02wh3rHgwnqoLAZcQvbfVFDZBOrIwsK75OCd%2BIPNYJPX%2B3WGPTNH6IkNQIL7i%2FfbCQ0QZuWwkvyTSAo6bC5jHh%2BkAz4i0kwQAS3GrHZgTpd%2BfhmwYBdK6UxFLFvnSThAfWylLUs4Tr%2B6862iU3pVuywtpb0%2FLGT5LAoPfEG%2FhAd%2BxKa%2BXPqX9ZivuFpXbtmFKltC6WdZCdVnq%2BZn7qhQj0ZPvx%2BoGTfeLkxjRpGHowXrYpUUkt5lPOTAus%2F1kanfYLU%2FBqWPhufk4IGtTjT9rGZhoZQcxHwxNri4kZanmcdA%2BrvdaF1iJtIh8HMKBKe7vUrth2rC7qHk63b%2BFEyhlvMEajHWw6zPhZOmrQkFteapAnKvXwIBoV149uqVGIJC8byFo9T0XnMRJ9Bg%3D%3D&amp;forwarderC=JTdCJTIyYWNjb21tb2RhdGlvblBvc2l0aW9uJTIyJTNBMyUyQyUyMmxpbmtMb2NhdGlvbiUyMiUzQSUyMkNIQU1QSU9OX0RFQUwlMjIlMkMlMjJwYWdlQ29udGFpbmVyJTIyJTNBJTIyTUFJTiUyMiUyQyUyMnBhZ2VOdW1iZXIlMjIlM0ExJTJDJTIydmlld01vZGUlMjIlM0ElMjJTVEFOREFSRCUyMiUyQyUyMmNsaWNrb3V0U291cmNlJTIyJTNBJTIySVRFTV9MSVNUX0NIQU1QSU9OX0RFQUwlMjIlMkMlMjJjbGllbnRDb25uZWN0aW9uSWQlMjIlM0ElMjJXemJxTzFyUXhBbFhhMjExY1BSRkh2cnlIMFclMjIlMkMlMjJjbGllbnRTZXF1ZW5jZUlkJTIyJTNBMjI4JTJDJTIyY2xpY2tvdXRFdmVudElkJTIyJTNBJTIyZTNiODljMWYtMWYxMy00Y2NlLTliYWMtMzU4ZTVkM2IyZmUyJTIyJTdE</t>
-  </si>
-  <si>
-    <t>Lentoyhtiö</t>
-  </si>
-  <si>
-    <t>Meno lähtee</t>
-  </si>
-  <si>
-    <t>Meno perillä</t>
-  </si>
-  <si>
-    <t>Paluu lähtee</t>
-  </si>
-  <si>
-    <t>Paluu perillä</t>
-  </si>
-  <si>
-    <t>Kokonaishinta (4 hlö)</t>
-  </si>
-  <si>
-    <t>Varauslinkki</t>
-  </si>
-  <si>
     <t>Finnair</t>
   </si>
   <si>
@@ -113,12 +64,15 @@
     <t>16.40</t>
   </si>
   <si>
-    <t>969 €</t>
+    <t>973 €</t>
   </si>
   <si>
     <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221235--32317-0-12126-2608221640?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
   </si>
   <si>
+    <t>07.04.2026</t>
+  </si>
+  <si>
     <t>20.30</t>
   </si>
   <si>
@@ -135,6 +89,9 @@
   </si>
   <si>
     <t>19.00</t>
+  </si>
+  <si>
+    <t>1 045 €</t>
   </si>
   <si>
     <t>https://www.skyscanner.fihttps://www.skyscanner.fi/liikennevalineet/lennot/hel/pari/260815/260822/config/12126-2608151215--32317-0-10413-2608151420%7C10413-2608221505--32317-0-12126-2608221900?adultsv2=4&amp;cabinclass=economy&amp;childrenv2=&amp;ref=home&amp;rtn=1&amp;preferdirects=false&amp;outboundaltsenabled=false&amp;inboundaltsenabled=false</t>
@@ -144,9 +101,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -176,9 +130,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -484,7 +437,13 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="51" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -492,28 +451,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -521,28 +480,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -550,28 +509,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -579,121 +538,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1049</v>
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
